--- a/JsonConverter/ExcelFiles/CocktailRecipe.xlsx
+++ b/JsonConverter/ExcelFiles/CocktailRecipe.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="18720" windowHeight="11745"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="22545" windowHeight="11745"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -14,195 +14,285 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="63">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="93">
+  <x:si>
+    <x:t>Icon/Cocktail_Fail_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_SugarRush_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_FluffyDream_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_PianoWoman_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Mercuryblast_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_MoonBlast_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BlueFairy_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BloomLight_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Beer_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_CobaltVelvet_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_FringeWeaver_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Suplex_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_ZenStar_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Piledriver_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Brandtini_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_FrothyWater_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BleedingJane_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_CreviceSpike_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_SparkleStar_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Beer_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Fail_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Flanergide</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Optional</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BronsonExt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Karmotrine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PwdDelta</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Adelhyde</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>크레바스 스파이크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>머큐리 블라스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>션샤인 클라우드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_SunshineCloud_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_BleedingJane_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_CobaltVelvet_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_FringeWeaver_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_CreviceSpike_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Mercuryblast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_GrlzzlyTemple_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스파클 스타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 우먼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거트 펀치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블리딩 제인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파일 드라이버</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프린지 위버</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>브랜티니</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블루 페어리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코발트 벨벳</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슈가 러쉬</x:t>
+  </x:si>
+  <x:si>
+    <x:t>문 블라스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블룸 라이트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 맨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그리즐리 템플</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로씨 워터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수플렉스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>true</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마스블라스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배드 터치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>플러피 드림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>false</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F@####</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BadTouch_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Suplex_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_ZenStar_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_GutPunch_2</x:t>
+  </x:si>
   <x:si>
     <x:t>Cocktail_PianoMan_2</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocktail_Suplex_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_GutPunch_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_ZenStar_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BadTouch_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_CreviceSpike_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_SparkleStar_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_FringeWeaver_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BloomLight_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Mercuryblast_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_CobaltVelvet_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BleedingJane_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_SugarRush_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BlueFairy_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_MoonBlast_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_PianoWoman_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Piledriver_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Brandtini_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Mercryblast_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_FrothyWater_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_FluffyDream_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Beer_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Karmotrine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Optional</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Adelhyde</x:t>
-  </x:si>
-  <x:si>
-    <x:t>크레바스 스파이크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>션샤인 클라우드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Flanergide</x:t>
-  </x:si>
-  <x:si>
-    <x:t>머큐리 블라스트</x:t>
+    <x:t>맥주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Age</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
   </x:si>
   <x:si>
     <x:t>젠스타</x:t>
   </x:si>
   <x:si>
-    <x:t>맥주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
+    <x:t>Ice</x:t>
   </x:si>
   <x:si>
     <x:t>int</x:t>
   </x:si>
   <x:si>
-    <x:t>Age</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코발트 벨벳</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피아노 우먼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프린지 위버</x:t>
-  </x:si>
-  <x:si>
-    <x:t>문 블라스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파일 드라이버</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거트 펀치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블리딩 제인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슈가 러쉬</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수플렉스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>브랜티니</x:t>
-  </x:si>
-  <x:si>
-    <x:t>플러피 드림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배드 터치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스파클 스타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블룸 라이트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블루 페어리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피아노 맨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bool</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마스블라스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로씨 워터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그리즐리 템플</x:t>
+    <x:t>Icon/Cocktail_MoonBlast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_GutPunch_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_PianoWoman_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Piledriver_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_FluffyDream_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_SparkleStar_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Brandtini_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_FrothyWater_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_BadTouch_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_BlueFairy_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_BloomLight_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_SugarRush_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_PianoMan_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Marsblast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_GrlzzlyTemple_2</x:t>
   </x:si>
   <x:si>
     <x:t>Cocktail_SunshineCloud_2</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocktail_GrlzzlyTemple_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PwdDelta</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BronsonExt</x:t>
+    <x:t>Cocktail_Mersblast_2</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -381,7 +471,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="18">
+  <x:cellXfs count="20">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
@@ -476,6 +566,12 @@
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle xfId="0" builtinId="0"/>
@@ -1545,81 +1641,87 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
     </x:row>
-    <x:row r="2" spans="1:10" ht="12.300000000000001">
+    <x:row r="2" spans="1:11" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G2" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="H2" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="H2" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="J2" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K2" s="1" t="s">
+        <x:v>46</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:10" s="11" customFormat="1" ht="15.75" customHeight="1">
+    <x:row r="3" spans="1:11" s="11" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="10" t="s">
-        <x:v>32</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B3" s="10" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C3" s="12" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D3" s="13" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E3" s="13" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="D3" s="13" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="E3" s="13" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="F3" s="13" t="s">
-        <x:v>28</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G3" s="12" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H3" s="12" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="I3" s="11" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="J3" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H3" s="12" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="I3" s="11" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="J3" s="13" t="s">
-        <x:v>23</x:v>
+      <x:c r="K3" s="12" t="s">
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>44</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C4" s="14">
         <x:v>2</x:v>
@@ -1636,25 +1738,27 @@
       <x:c r="G4" s="4">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H4" s="4" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I4" s="4" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J4" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K4" s="4"/>
+      <x:c r="H4" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="I4" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="J4" s="18" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K4" s="3" t="s">
+        <x:v>87</x:v>
+      </x:c>
       <x:c r="L4" s="4"/>
       <x:c r="M4" s="4"/>
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>51</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C5" s="15">
         <x:v>2</x:v>
@@ -1671,25 +1775,27 @@
       <x:c r="G5" s="4">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H5" s="4" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I5" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J5" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K5" s="4"/>
+      <x:c r="H5" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="I5" s="18" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="J5" s="18" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K5" s="3" t="s">
+        <x:v>81</x:v>
+      </x:c>
       <x:c r="L5" s="4"/>
       <x:c r="M5" s="4"/>
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C6" s="15">
         <x:v>4</x:v>
@@ -1706,25 +1812,27 @@
       <x:c r="G6" s="4">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H6" s="4" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I6" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J6" s="2" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K6" s="4"/>
+      <x:c r="H6" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="I6" s="18" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="J6" s="18" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K6" s="5" t="s">
+        <x:v>85</x:v>
+      </x:c>
       <x:c r="L6" s="4"/>
       <x:c r="M6" s="4"/>
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C7" s="17">
         <x:v>6</x:v>
@@ -1741,25 +1849,27 @@
       <x:c r="G7" s="4">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H7" s="4" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I7" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J7" s="4" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K7" s="4"/>
+      <x:c r="H7" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="I7" s="18" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="J7" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="K7" s="6" t="s">
+        <x:v>82</x:v>
+      </x:c>
       <x:c r="L7" s="4"/>
       <x:c r="M7" s="4"/>
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s">
-        <x:v>15</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C8" s="17">
         <x:v>5</x:v>
@@ -1776,22 +1886,24 @@
       <x:c r="G8" s="4">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H8" s="4" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I8" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J8" s="4" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K8" s="4"/>
+      <x:c r="H8" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="I8" s="18" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="J8" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="K8" s="6" t="s">
+        <x:v>78</x:v>
+      </x:c>
       <x:c r="L8" s="4"/>
       <x:c r="M8" s="4"/>
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>41</x:v>
@@ -1811,25 +1923,27 @@
       <x:c r="G9" s="4">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H9" s="4" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I9" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J9" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K9" s="4"/>
+      <x:c r="H9" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="I9" s="18" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="J9" s="18" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K9" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
       <x:c r="L9" s="4"/>
       <x:c r="M9" s="4"/>
     </x:row>
     <x:row r="10" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C10" s="14">
         <x:v>0</x:v>
@@ -1846,25 +1960,27 @@
       <x:c r="G10" s="4">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H10" s="4" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I10" s="4" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J10" s="4" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K10" s="4"/>
+      <x:c r="H10" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="I10" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="J10" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="K10" s="1" t="s">
+        <x:v>79</x:v>
+      </x:c>
       <x:c r="L10" s="4"/>
       <x:c r="M10" s="4"/>
     </x:row>
     <x:row r="11" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A11" s="6" t="s">
-        <x:v>1</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B11" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C11" s="14">
         <x:v>0</x:v>
@@ -1881,25 +1997,27 @@
       <x:c r="G11" s="4">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H11" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I11" s="4" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J11" s="4" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K11" s="4"/>
+      <x:c r="H11" s="18" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="I11" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="J11" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="K11" s="6" t="s">
+        <x:v>11</x:v>
+      </x:c>
       <x:c r="L11" s="4"/>
       <x:c r="M11" s="4"/>
     </x:row>
     <x:row r="12" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A12" s="6" t="s">
-        <x:v>20</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B12" s="6" t="s">
-        <x:v>47</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C12" s="16">
         <x:v>3</x:v>
@@ -1916,25 +2034,27 @@
       <x:c r="G12" s="4">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H12" s="4" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I12" s="4" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J12" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K12" s="4"/>
+      <x:c r="H12" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="I12" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="J12" s="18" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K12" s="6" t="s">
+        <x:v>80</x:v>
+      </x:c>
       <x:c r="L12" s="4"/>
       <x:c r="M12" s="4"/>
     </x:row>
     <x:row r="13" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A13" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C13" s="17">
         <x:v>0</x:v>
@@ -1951,25 +2071,27 @@
       <x:c r="G13" s="4">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H13" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I13" s="4" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J13" s="4" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K13" s="4"/>
+      <x:c r="H13" s="18" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="I13" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="J13" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="K13" s="6" t="s">
+        <x:v>84</x:v>
+      </x:c>
       <x:c r="L13" s="4"/>
       <x:c r="M13" s="4"/>
     </x:row>
     <x:row r="14" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A14" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B14" s="7" t="s">
-        <x:v>30</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C14" s="14">
         <x:v>4</x:v>
@@ -1986,22 +2108,24 @@
       <x:c r="G14" s="4">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H14" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I14" s="4" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J14" s="4" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K14" s="4"/>
+      <x:c r="H14" s="18" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="I14" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="J14" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="K14" s="6" t="s">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="L14" s="4"/>
       <x:c r="M14" s="4"/>
     </x:row>
     <x:row r="15" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A15" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
         <x:v>52</x:v>
@@ -2021,25 +2145,27 @@
       <x:c r="G15" s="4">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H15" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I15" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J15" s="4" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K15" s="4"/>
+      <x:c r="H15" s="18" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="I15" s="18" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="J15" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="K15" s="6" t="s">
+        <x:v>86</x:v>
+      </x:c>
       <x:c r="L15" s="4"/>
       <x:c r="M15" s="4"/>
     </x:row>
-    <x:row r="16" spans="1:10" ht="15.75" customHeight="1">
+    <x:row r="16" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A16" s="6" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B16" s="7" t="s">
-        <x:v>31</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C16" s="15">
         <x:v>1</x:v>
@@ -2056,22 +2182,25 @@
       <x:c r="G16" s="2">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H16" s="2" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I16" s="2" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J16" s="2" t="b">
-        <x:v>0</x:v>
+      <x:c r="H16" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="I16" s="18" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="J16" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="K16" s="6" t="s">
+        <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:10" ht="15.75" customHeight="1">
+    <x:row r="17" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A17" s="6" t="s">
-        <x:v>19</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B17" s="7" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C17" s="15">
         <x:v>1</x:v>
@@ -2088,22 +2217,25 @@
       <x:c r="G17" s="2">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H17" s="2" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I17" s="2" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J17" s="2" t="b">
-        <x:v>0</x:v>
+      <x:c r="H17" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="I17" s="18" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="J17" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="K17" s="6" t="s">
+        <x:v>83</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:10" ht="15.75" customHeight="1">
+    <x:row r="18" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A18" s="6" t="s">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B18" s="7" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C18" s="15">
         <x:v>2</x:v>
@@ -2120,22 +2252,25 @@
       <x:c r="G18" s="2">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H18" s="2" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I18" s="2" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J18" s="2" t="b">
-        <x:v>0</x:v>
+      <x:c r="H18" s="18" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="I18" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="J18" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="K18" s="6" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:10" ht="15.75" customHeight="1">
+    <x:row r="19" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A19" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B19" s="7" t="s">
-        <x:v>38</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C19" s="15">
         <x:v>1</x:v>
@@ -2152,22 +2287,25 @@
       <x:c r="G19" s="2">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="H19" s="2" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I19" s="2" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J19" s="2" t="b">
-        <x:v>0</x:v>
+      <x:c r="H19" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="I19" s="18" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="J19" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="K19" s="6" t="s">
+        <x:v>35</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:10" ht="15.75" customHeight="1">
+    <x:row r="20" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A20" s="6" t="s">
-        <x:v>14</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B20" s="7" t="s">
-        <x:v>39</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C20" s="15">
         <x:v>6</x:v>
@@ -2184,22 +2322,25 @@
       <x:c r="G20" s="2">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H20" s="2" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I20" s="2" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J20" s="2" t="b">
-        <x:v>0</x:v>
+      <x:c r="H20" s="18" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="I20" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="J20" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="K20" s="6" t="s">
+        <x:v>76</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:10" ht="15.75" customHeight="1">
+    <x:row r="21" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A21" s="6" t="s">
-        <x:v>60</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B21" s="7" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C21" s="15">
         <x:v>3</x:v>
@@ -2216,22 +2357,25 @@
       <x:c r="G21" s="2">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H21" s="2" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I21" s="2" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J21" s="2" t="b">
-        <x:v>0</x:v>
+      <x:c r="H21" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="I21" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="J21" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="K21" s="6" t="s">
+        <x:v>38</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:10" ht="15.75" customHeight="1">
+    <x:row r="22" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A22" s="6" t="s">
-        <x:v>59</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B22" s="7" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C22" s="15">
         <x:v>2</x:v>
@@ -2248,22 +2392,25 @@
       <x:c r="G22" s="2">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H22" s="2" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I22" s="2" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J22" s="2" t="b">
-        <x:v>1</x:v>
+      <x:c r="H22" s="18" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="I22" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="J22" s="18" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K22" s="6" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:10" ht="15.75" customHeight="1">
+    <x:row r="23" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A23" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B23" s="7" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C23" s="15">
         <x:v>0</x:v>
@@ -2280,19 +2427,22 @@
       <x:c r="G23" s="2">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H23" s="2" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I23" s="2" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J23" s="2" t="b">
-        <x:v>1</x:v>
+      <x:c r="H23" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="I23" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="J23" s="18" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K23" s="6" t="s">
+        <x:v>36</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:10" ht="15.75" customHeight="1">
+    <x:row r="24" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A24" s="6" t="s">
-        <x:v>9</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B24" s="7" t="s">
         <x:v>29</x:v>
@@ -2312,19 +2462,22 @@
       <x:c r="G24" s="2">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H24" s="2" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I24" s="2" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J24" s="2" t="b">
-        <x:v>0</x:v>
+      <x:c r="H24" s="18" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="I24" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="J24" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="K24" s="6" t="s">
+        <x:v>37</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:10" ht="15.75" customHeight="1">
+    <x:row r="25" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A25" s="6" t="s">
-        <x:v>0</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B25" s="7" t="s">
         <x:v>54</x:v>
@@ -2344,19 +2497,22 @@
       <x:c r="G25" s="2">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H25" s="2" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I25" s="2" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J25" s="2" t="b">
-        <x:v>0</x:v>
+      <x:c r="H25" s="18" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="I25" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="J25" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="K25" s="6" t="s">
+        <x:v>88</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:10" ht="15.75" customHeight="1">
+    <x:row r="26" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A26" s="6" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B26" s="8" t="s">
         <x:v>42</x:v>
@@ -2376,22 +2532,25 @@
       <x:c r="G26" s="2">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H26" s="2" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I26" s="2" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J26" s="2" t="b">
-        <x:v>0</x:v>
+      <x:c r="H26" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="I26" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="J26" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="K26" s="6" t="s">
+        <x:v>33</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:10" ht="15.75" customHeight="1">
+    <x:row r="27" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A27" s="6" t="s">
-        <x:v>18</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B27" s="8" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C27" s="16">
         <x:v>0</x:v>
@@ -2408,20 +2567,30 @@
       <x:c r="G27" s="2">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H27" s="2" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I27" s="2" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J27" s="2" t="b">
-        <x:v>0</x:v>
+      <x:c r="H27" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="I27" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="J27" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="K27" s="6" t="s">
+        <x:v>89</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A28" s="6"/>
-      <x:c r="B28" s="8"/>
+    <x:row r="28" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A28" s="19" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B28" s="8" t="s">
+        <x:v>64</x:v>
+      </x:c>
       <x:c r="C28" s="8"/>
+      <x:c r="K28" s="2" t="s">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A29" s="6"/>

--- a/JsonConverter/ExcelFiles/CocktailRecipe.xlsx
+++ b/JsonConverter/ExcelFiles/CocktailRecipe.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="22545" windowHeight="11745"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="24240" windowHeight="13680"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -16,123 +16,159 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="93">
   <x:si>
+    <x:t>Cocktail_BadTouch_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_ZenStar_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_GutPunch_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Suplex_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_PianoMan_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Piledriver_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_FrothyWater_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Brandtini_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_FringeWeaver_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BleedingJane_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_CreviceSpike_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_PianoWoman_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_SparkleStar_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Mersblast_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_MoonBlast_2</x:t>
+  </x:si>
+  <x:si>
     <x:t>Icon/Cocktail_Fail_1</x:t>
   </x:si>
   <x:si>
+    <x:t>Cocktail_BloomLight_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Mercuryblast_2</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cocktail_SugarRush_2</x:t>
   </x:si>
   <x:si>
+    <x:t>Cocktail_BlueFairy_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Beer_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cocktail_FluffyDream_2</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocktail_PianoWoman_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Mercuryblast_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_MoonBlast_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BlueFairy_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BloomLight_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Beer_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>Cocktail_CobaltVelvet_2</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocktail_FringeWeaver_2</x:t>
-  </x:si>
-  <x:si>
     <x:t>Icon/Cocktail_Suplex_1</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Cocktail_ZenStar_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocktail_Piledriver_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Brandtini_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_FrothyWater_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BleedingJane_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_CreviceSpike_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_SparkleStar_2</x:t>
+    <x:t>Cocktail_Fail_2</x:t>
   </x:si>
   <x:si>
     <x:t>Cocktail_Beer_2</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocktail_Fail_2</x:t>
+    <x:t>젠스타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맥주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Age</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Mercuryblast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_SunshineCloud_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_CreviceSpike_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_CobaltVelvet_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_FringeWeaver_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_GrlzzlyTemple_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_BleedingJane_1</x:t>
   </x:si>
   <x:si>
     <x:t>Flanergide</x:t>
   </x:si>
   <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Karmotrine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>크레바스 스파이크</x:t>
+  </x:si>
+  <x:si>
     <x:t>Optional</x:t>
   </x:si>
   <x:si>
     <x:t>BronsonExt</x:t>
   </x:si>
   <x:si>
-    <x:t>Karmotrine</x:t>
-  </x:si>
-  <x:si>
     <x:t>PwdDelta</x:t>
   </x:si>
   <x:si>
+    <x:t>션샤인 클라우드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>머큐리 블라스트</x:t>
+  </x:si>
+  <x:si>
     <x:t>Adelhyde</x:t>
   </x:si>
   <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>크레바스 스파이크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>머큐리 블라스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>션샤인 클라우드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_SunshineCloud_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_BleedingJane_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_CobaltVelvet_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_FringeWeaver_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_CreviceSpike_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Mercuryblast_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_GrlzzlyTemple_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>스파클 스타</x:t>
   </x:si>
   <x:si>
@@ -151,148 +187,112 @@
     <x:t>파일 드라이버</x:t>
   </x:si>
   <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블루 페어리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코발트 벨벳</x:t>
+  </x:si>
+  <x:si>
     <x:t>프린지 위버</x:t>
   </x:si>
   <x:si>
-    <x:t>string</x:t>
+    <x:t>슈가 러쉬</x:t>
+  </x:si>
+  <x:si>
+    <x:t>문 블라스트</x:t>
   </x:si>
   <x:si>
     <x:t>브랜티니</x:t>
   </x:si>
   <x:si>
-    <x:t>블루 페어리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코발트 벨벳</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슈가 러쉬</x:t>
-  </x:si>
-  <x:si>
-    <x:t>문 블라스트</x:t>
-  </x:si>
-  <x:si>
     <x:t>블룸 라이트</x:t>
   </x:si>
   <x:si>
     <x:t>Name</x:t>
   </x:si>
   <x:si>
+    <x:t>false</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로씨 워터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마스블라스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F@####</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수플렉스</x:t>
+  </x:si>
+  <x:si>
     <x:t>피아노 맨</x:t>
   </x:si>
   <x:si>
     <x:t>그리즐리 템플</x:t>
   </x:si>
   <x:si>
-    <x:t>프로씨 워터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수플렉스</x:t>
-  </x:si>
-  <x:si>
     <x:t>true</x:t>
   </x:si>
   <x:si>
-    <x:t>마스블라스트</x:t>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>플러피 드림</x:t>
   </x:si>
   <x:si>
     <x:t>배드 터치</x:t>
   </x:si>
   <x:si>
-    <x:t>플러피 드림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>false</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>F@####</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BadTouch_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Suplex_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_ZenStar_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_GutPunch_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_PianoMan_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맥주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Age</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>젠스타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
+    <x:t>Icon/Cocktail_FluffyDream_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_SparkleStar_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Brandtini_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_GutPunch_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Piledriver_1</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Cocktail_MoonBlast_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Cocktail_GutPunch_1</x:t>
+    <x:t>Icon/Cocktail_FrothyWater_1</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Cocktail_PianoWoman_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Cocktail_Piledriver_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_FluffyDream_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_SparkleStar_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Brandtini_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_FrothyWater_1</x:t>
+    <x:t>Cocktail_SunshineCloud_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_GrlzzlyTemple_2</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Cocktail_BadTouch_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Cocktail_BlueFairy_1</x:t>
+    <x:t>Icon/Cocktail_SugarRush_1</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Cocktail_BloomLight_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Cocktail_SugarRush_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>Icon/Cocktail_PianoMan_1</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Cocktail_Marsblast_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocktail_GrlzzlyTemple_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_SunshineCloud_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Mersblast_2</x:t>
+    <x:t xml:space="preserve">Icon/Cocktail_BlueFairy_1 </x:t>
   </x:si>
 </x:sst>
 </file>
@@ -582,7 +582,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -665,7 +664,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -700,7 +698,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -745,7 +742,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -789,7 +785,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -874,7 +869,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -895,7 +889,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -926,7 +919,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1641,87 +1633,87 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:11" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>43</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J2" s="2" t="s">
-        <x:v>43</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K2" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11" s="11" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="10" t="s">
-        <x:v>72</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B3" s="10" t="s">
-        <x:v>53</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C3" s="12" t="s">
-        <x:v>26</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D3" s="13" t="s">
-        <x:v>23</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E3" s="13" t="s">
-        <x:v>25</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F3" s="13" t="s">
-        <x:v>21</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G3" s="12" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H3" s="12" t="s">
-        <x:v>74</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I3" s="11" t="s">
-        <x:v>71</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="J3" s="13" t="s">
-        <x:v>22</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K3" s="12" t="s">
-        <x:v>27</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>50</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C4" s="14">
         <x:v>2</x:v>
@@ -1739,26 +1731,26 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H4" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="I4" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J4" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K4" s="3" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="L4" s="4"/>
       <x:c r="M4" s="4"/>
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>39</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C5" s="15">
         <x:v>2</x:v>
@@ -1776,26 +1768,26 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H5" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="I5" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J5" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K5" s="3" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="L5" s="4"/>
       <x:c r="M5" s="4"/>
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>6</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C6" s="15">
         <x:v>4</x:v>
@@ -1813,26 +1805,26 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H6" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="I6" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J6" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K6" s="5" t="s">
-        <x:v>85</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="L6" s="4"/>
       <x:c r="M6" s="4"/>
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>14</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>47</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C7" s="17">
         <x:v>6</x:v>
@@ -1850,26 +1842,26 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H7" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="I7" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J7" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="K7" s="6" t="s">
-        <x:v>82</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="L7" s="4"/>
       <x:c r="M7" s="4"/>
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>40</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C8" s="17">
         <x:v>5</x:v>
@@ -1887,26 +1879,26 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H8" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="I8" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J8" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="K8" s="6" t="s">
-        <x:v>78</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="L8" s="4"/>
       <x:c r="M8" s="4"/>
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C9" s="17">
         <x:v>0</x:v>
@@ -1924,26 +1916,26 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H9" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="I9" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J9" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K9" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="L9" s="4"/>
       <x:c r="M9" s="4"/>
     </x:row>
     <x:row r="10" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C10" s="14">
         <x:v>0</x:v>
@@ -1961,26 +1953,26 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="H10" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="I10" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J10" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="K10" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="L10" s="4"/>
       <x:c r="M10" s="4"/>
     </x:row>
     <x:row r="11" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A11" s="6" t="s">
-        <x:v>66</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="6" t="s">
-        <x:v>57</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C11" s="14">
         <x:v>0</x:v>
@@ -1998,26 +1990,26 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H11" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="I11" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J11" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="K11" s="6" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="L11" s="4"/>
       <x:c r="M11" s="4"/>
     </x:row>
     <x:row r="12" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A12" s="6" t="s">
-        <x:v>2</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B12" s="6" t="s">
-        <x:v>61</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C12" s="16">
         <x:v>3</x:v>
@@ -2035,26 +2027,26 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H12" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="I12" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J12" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K12" s="6" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="L12" s="4"/>
       <x:c r="M12" s="4"/>
     </x:row>
     <x:row r="13" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A13" s="6" t="s">
-        <x:v>65</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C13" s="17">
         <x:v>0</x:v>
@@ -2072,26 +2064,26 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="H13" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="I13" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J13" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="K13" s="6" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="L13" s="4"/>
       <x:c r="M13" s="4"/>
     </x:row>
     <x:row r="14" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A14" s="6" t="s">
-        <x:v>67</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B14" s="7" t="s">
-        <x:v>73</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C14" s="14">
         <x:v>4</x:v>
@@ -2109,26 +2101,26 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="H14" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="I14" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J14" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="K14" s="6" t="s">
-        <x:v>12</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="L14" s="4"/>
       <x:c r="M14" s="4"/>
     </x:row>
     <x:row r="15" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A15" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C15" s="14">
         <x:v>4</x:v>
@@ -2146,26 +2138,26 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H15" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="I15" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J15" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="K15" s="6" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="L15" s="4"/>
       <x:c r="M15" s="4"/>
     </x:row>
     <x:row r="16" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A16" s="6" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B16" s="7" t="s">
-        <x:v>70</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C16" s="15">
         <x:v>1</x:v>
@@ -2183,24 +2175,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="H16" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="I16" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J16" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="K16" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A17" s="6" t="s">
-        <x:v>15</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B17" s="7" t="s">
-        <x:v>56</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C17" s="15">
         <x:v>1</x:v>
@@ -2218,13 +2210,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H17" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="I17" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J17" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="K17" s="6" t="s">
         <x:v>83</x:v>
@@ -2232,10 +2224,10 @@
     </x:row>
     <x:row r="18" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A18" s="6" t="s">
-        <x:v>9</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B18" s="7" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C18" s="15">
         <x:v>2</x:v>
@@ -2253,24 +2245,24 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="H18" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="I18" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J18" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="K18" s="6" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A19" s="6" t="s">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B19" s="7" t="s">
-        <x:v>45</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C19" s="15">
         <x:v>1</x:v>
@@ -2288,24 +2280,24 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="H19" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="I19" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J19" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="K19" s="6" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A20" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B20" s="7" t="s">
-        <x:v>51</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C20" s="15">
         <x:v>6</x:v>
@@ -2323,24 +2315,24 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H20" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="I20" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J20" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="K20" s="6" t="s">
-        <x:v>76</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A21" s="6" t="s">
-        <x:v>90</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B21" s="7" t="s">
-        <x:v>55</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C21" s="15">
         <x:v>3</x:v>
@@ -2358,13 +2350,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H21" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="I21" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J21" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="K21" s="6" t="s">
         <x:v>38</x:v>
@@ -2372,10 +2364,10 @@
     </x:row>
     <x:row r="22" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A22" s="6" t="s">
-        <x:v>91</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B22" s="7" t="s">
-        <x:v>30</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C22" s="15">
         <x:v>2</x:v>
@@ -2393,24 +2385,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H22" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="I22" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J22" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K22" s="6" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A23" s="6" t="s">
-        <x:v>17</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B23" s="7" t="s">
-        <x:v>28</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C23" s="15">
         <x:v>0</x:v>
@@ -2428,24 +2420,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H23" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="I23" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J23" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K23" s="6" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A24" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B24" s="7" t="s">
-        <x:v>29</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C24" s="15">
         <x:v>1</x:v>
@@ -2463,24 +2455,24 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H24" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="I24" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J24" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="K24" s="6" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A25" s="6" t="s">
-        <x:v>69</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B25" s="7" t="s">
-        <x:v>54</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C25" s="15">
         <x:v>2</x:v>
@@ -2498,24 +2490,24 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H25" s="18" t="s">
-        <x:v>58</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="I25" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J25" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="K25" s="6" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A26" s="6" t="s">
-        <x:v>16</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B26" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C26" s="16">
         <x:v>0</x:v>
@@ -2533,24 +2525,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H26" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="I26" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J26" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="K26" s="6" t="s">
-        <x:v>33</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A27" s="6" t="s">
-        <x:v>92</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B27" s="8" t="s">
-        <x:v>59</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C27" s="16">
         <x:v>0</x:v>
@@ -2568,28 +2560,28 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H27" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="I27" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J27" s="18" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="K27" s="6" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A28" s="19" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B28" s="8" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C28" s="8"/>
       <x:c r="K28" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/CocktailRecipe.xlsx
+++ b/JsonConverter/ExcelFiles/CocktailRecipe.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="24240" windowHeight="13680"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="20610" windowHeight="11190"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -16,79 +16,157 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="93">
   <x:si>
+    <x:t>Cocktail_GutPunch_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_ZenStar_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Suplex_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_PianoMan_2</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cocktail_BadTouch_2</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocktail_ZenStar_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_GutPunch_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Suplex_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_PianoMan_2</x:t>
-  </x:si>
-  <x:si>
     <x:t>Cocktail_Piledriver_2</x:t>
   </x:si>
   <x:si>
+    <x:t>Cocktail_BleedingJane_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_FringeWeaver_2</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cocktail_FrothyWater_2</x:t>
   </x:si>
   <x:si>
+    <x:t>Cocktail_CreviceSpike_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_PianoWoman_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_SparkleStar_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Mersblast_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_MoonBlast_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BloomLight_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Fail_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cocktail_Brandtini_2</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocktail_FringeWeaver_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BleedingJane_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_CreviceSpike_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_PianoWoman_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_SparkleStar_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Mersblast_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_MoonBlast_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Fail_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BloomLight_2</x:t>
+    <x:t>Cocktail_SugarRush_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_CobaltVelvet_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Suplex_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_ZenStar_1</x:t>
   </x:si>
   <x:si>
     <x:t>Cocktail_Mercuryblast_2</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocktail_SugarRush_2</x:t>
+    <x:t>Icon/Cocktail_Beer_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_FluffyDream_2</x:t>
   </x:si>
   <x:si>
     <x:t>Cocktail_BlueFairy_2</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Cocktail_Beer_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_FluffyDream_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_CobaltVelvet_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Suplex_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_ZenStar_1</x:t>
+    <x:t>스파클 스타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프린지 위버</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로씨 워터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마스블라스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>false</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F@####</x:t>
+  </x:si>
+  <x:si>
+    <x:t>문 블라스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수플렉스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 맨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블루 페어리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파일 드라이버</x:t>
+  </x:si>
+  <x:si>
+    <x:t>브랜티니</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 우먼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거트 펀치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블리딩 제인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코발트 벨벳</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슈가 러쉬</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블룸 라이트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>true</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>플러피 드림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배드 터치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그리즐리 템플</x:t>
   </x:si>
   <x:si>
     <x:t>Cocktail_Fail_2</x:t>
@@ -97,43 +175,49 @@
     <x:t>Cocktail_Beer_2</x:t>
   </x:si>
   <x:si>
+    <x:t>Age</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
     <x:t>젠스타</x:t>
   </x:si>
   <x:si>
     <x:t>맥주</x:t>
   </x:si>
   <x:si>
-    <x:t>Age</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ice</x:t>
-  </x:si>
-  <x:si>
     <x:t>Id</x:t>
   </x:si>
   <x:si>
-    <x:t>int</x:t>
+    <x:t>Icon/Cocktail_SunshineCloud_1</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Cocktail_Mercuryblast_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Cocktail_SunshineCloud_1</x:t>
+    <x:t>Icon/Cocktail_CobaltVelvet_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_BleedingJane_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_FringeWeaver_1</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Cocktail_CreviceSpike_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Cocktail_CobaltVelvet_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_FringeWeaver_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>Icon/Cocktail_GrlzzlyTemple_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Cocktail_BleedingJane_1</x:t>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>크레바스 스파이크</x:t>
   </x:si>
   <x:si>
     <x:t>Flanergide</x:t>
@@ -145,154 +229,70 @@
     <x:t>Karmotrine</x:t>
   </x:si>
   <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>크레바스 스파이크</x:t>
+    <x:t>BronsonExt</x:t>
   </x:si>
   <x:si>
     <x:t>Optional</x:t>
   </x:si>
   <x:si>
-    <x:t>BronsonExt</x:t>
-  </x:si>
-  <x:si>
     <x:t>PwdDelta</x:t>
   </x:si>
   <x:si>
+    <x:t>머큐리 블라스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Adelhyde</x:t>
+  </x:si>
+  <x:si>
     <x:t>션샤인 클라우드</x:t>
   </x:si>
   <x:si>
-    <x:t>머큐리 블라스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Adelhyde</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스파클 스타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피아노 우먼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거트 펀치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블리딩 제인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bool</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파일 드라이버</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블루 페어리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코발트 벨벳</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프린지 위버</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슈가 러쉬</x:t>
-  </x:si>
-  <x:si>
-    <x:t>문 블라스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>브랜티니</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블룸 라이트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>false</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로씨 워터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마스블라스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>F@####</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수플렉스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피아노 맨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그리즐리 템플</x:t>
-  </x:si>
-  <x:si>
-    <x:t>true</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>플러피 드림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배드 터치</x:t>
+    <x:t>Icon/Cocktail_GutPunch_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Piledriver_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_MoonBlast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_SparkleStar_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_FrothyWater_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Brandtini_1</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Cocktail_FluffyDream_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Cocktail_SparkleStar_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Brandtini_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_GutPunch_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Piledriver_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_MoonBlast_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_FrothyWater_1</x:t>
+    <x:t>Icon/Cocktail_Marsblast_1</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Cocktail_PianoWoman_1</x:t>
   </x:si>
   <x:si>
+    <x:t>Icon/Cocktail_SugarRush_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Icon/Cocktail_BlueFairy_1 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_BloomLight_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_GrlzzlyTemple_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_BadTouch_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cocktail_SunshineCloud_2</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocktail_GrlzzlyTemple_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_BadTouch_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_SugarRush_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_BloomLight_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>Icon/Cocktail_PianoMan_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Marsblast_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Icon/Cocktail_BlueFairy_1 </x:t>
   </x:si>
 </x:sst>
 </file>
@@ -582,6 +582,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -664,6 +665,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -698,6 +700,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -742,6 +745,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -785,6 +789,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -869,6 +874,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -889,6 +895,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -919,6 +926,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1633,87 +1641,87 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:11" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="J2" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="K2" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11" s="11" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="10" t="s">
-        <x:v>31</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B3" s="10" t="s">
-        <x:v>65</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C3" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D3" s="13" t="s">
-        <x:v>46</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E3" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F3" s="13" t="s">
-        <x:v>40</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G3" s="12" t="s">
-        <x:v>42</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H3" s="12" t="s">
-        <x:v>30</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I3" s="11" t="s">
-        <x:v>29</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J3" s="13" t="s">
-        <x:v>45</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="K3" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>61</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C4" s="14">
         <x:v>2</x:v>
@@ -1731,26 +1739,26 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H4" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I4" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J4" s="18" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K4" s="3" t="s">
-        <x:v>88</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="L4" s="4"/>
       <x:c r="M4" s="4"/>
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>51</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C5" s="15">
         <x:v>2</x:v>
@@ -1768,26 +1776,26 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H5" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I5" s="18" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J5" s="18" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K5" s="3" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="L5" s="4"/>
       <x:c r="M5" s="4"/>
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>58</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C6" s="15">
         <x:v>4</x:v>
@@ -1805,26 +1813,26 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H6" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I6" s="18" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J6" s="18" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K6" s="5" t="s">
-        <x:v>92</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="L6" s="4"/>
       <x:c r="M6" s="4"/>
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>63</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C7" s="17">
         <x:v>6</x:v>
@@ -1842,26 +1850,26 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H7" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I7" s="18" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J7" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K7" s="6" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="L7" s="4"/>
       <x:c r="M7" s="4"/>
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>52</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C8" s="17">
         <x:v>5</x:v>
@@ -1879,26 +1887,26 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H8" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I8" s="18" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J8" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K8" s="6" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="L8" s="4"/>
       <x:c r="M8" s="4"/>
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C9" s="17">
         <x:v>0</x:v>
@@ -1916,16 +1924,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H9" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I9" s="18" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J9" s="18" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K9" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="L9" s="4"/>
       <x:c r="M9" s="4"/>
@@ -1935,7 +1943,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C10" s="14">
         <x:v>0</x:v>
@@ -1953,26 +1961,26 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="H10" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I10" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J10" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K10" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="L10" s="4"/>
       <x:c r="M10" s="4"/>
     </x:row>
     <x:row r="11" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A11" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B11" s="6" t="s">
-        <x:v>70</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C11" s="14">
         <x:v>0</x:v>
@@ -1990,26 +1998,26 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H11" s="18" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="I11" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J11" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K11" s="6" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="L11" s="4"/>
       <x:c r="M11" s="4"/>
     </x:row>
     <x:row r="12" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A12" s="6" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B12" s="6" t="s">
-        <x:v>75</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C12" s="16">
         <x:v>3</x:v>
@@ -2027,26 +2035,26 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H12" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I12" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J12" s="18" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K12" s="6" t="s">
-        <x:v>77</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="L12" s="4"/>
       <x:c r="M12" s="4"/>
     </x:row>
     <x:row r="13" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A13" s="6" t="s">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C13" s="17">
         <x:v>0</x:v>
@@ -2064,16 +2072,16 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="H13" s="18" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="I13" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J13" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K13" s="6" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="L13" s="4"/>
       <x:c r="M13" s="4"/>
@@ -2083,7 +2091,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B14" s="7" t="s">
-        <x:v>27</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C14" s="14">
         <x:v>4</x:v>
@@ -2101,26 +2109,26 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="H14" s="18" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="I14" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J14" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K14" s="6" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L14" s="4"/>
       <x:c r="M14" s="4"/>
     </x:row>
     <x:row r="15" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A15" s="6" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C15" s="14">
         <x:v>4</x:v>
@@ -2138,26 +2146,26 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H15" s="18" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="I15" s="18" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J15" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K15" s="6" t="s">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="L15" s="4"/>
       <x:c r="M15" s="4"/>
     </x:row>
     <x:row r="16" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A16" s="6" t="s">
-        <x:v>26</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B16" s="7" t="s">
-        <x:v>28</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C16" s="15">
         <x:v>1</x:v>
@@ -2175,24 +2183,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="H16" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I16" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J16" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K16" s="6" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A17" s="6" t="s">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B17" s="7" t="s">
-        <x:v>67</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C17" s="15">
         <x:v>1</x:v>
@@ -2210,24 +2218,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H17" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I17" s="18" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J17" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K17" s="6" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A18" s="6" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B18" s="7" t="s">
-        <x:v>59</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C18" s="15">
         <x:v>2</x:v>
@@ -2245,24 +2253,24 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="H18" s="18" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="I18" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J18" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K18" s="6" t="s">
-        <x:v>36</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A19" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B19" s="7" t="s">
-        <x:v>60</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C19" s="15">
         <x:v>1</x:v>
@@ -2280,24 +2288,24 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="H19" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I19" s="18" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J19" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K19" s="6" t="s">
-        <x:v>37</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A20" s="6" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B20" s="7" t="s">
-        <x:v>62</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C20" s="15">
         <x:v>6</x:v>
@@ -2315,24 +2323,24 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H20" s="18" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="I20" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J20" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K20" s="6" t="s">
-        <x:v>82</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A21" s="6" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B21" s="7" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C21" s="15">
         <x:v>3</x:v>
@@ -2350,24 +2358,24 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H21" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I21" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J21" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K21" s="6" t="s">
-        <x:v>38</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A22" s="6" t="s">
-        <x:v>85</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B22" s="7" t="s">
-        <x:v>48</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C22" s="15">
         <x:v>2</x:v>
@@ -2385,24 +2393,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H22" s="18" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="I22" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J22" s="18" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K22" s="6" t="s">
-        <x:v>34</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A23" s="6" t="s">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B23" s="7" t="s">
-        <x:v>44</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C23" s="15">
         <x:v>0</x:v>
@@ -2420,24 +2428,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H23" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I23" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J23" s="18" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K23" s="6" t="s">
-        <x:v>35</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A24" s="6" t="s">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B24" s="7" t="s">
-        <x:v>49</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C24" s="15">
         <x:v>1</x:v>
@@ -2455,24 +2463,24 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H24" s="18" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="I24" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J24" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K24" s="6" t="s">
-        <x:v>33</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A25" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B25" s="7" t="s">
-        <x:v>71</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C25" s="15">
         <x:v>2</x:v>
@@ -2490,24 +2498,24 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H25" s="18" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="I25" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J25" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K25" s="6" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A26" s="6" t="s">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B26" s="8" t="s">
-        <x:v>54</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C26" s="16">
         <x:v>0</x:v>
@@ -2525,24 +2533,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H26" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I26" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J26" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K26" s="6" t="s">
-        <x:v>39</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A27" s="6" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B27" s="8" t="s">
-        <x:v>68</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C27" s="16">
         <x:v>0</x:v>
@@ -2560,24 +2568,24 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H27" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I27" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J27" s="18" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K27" s="6" t="s">
-        <x:v>91</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A28" s="19" t="s">
-        <x:v>25</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B28" s="8" t="s">
-        <x:v>69</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C28" s="8"/>
       <x:c r="K28" s="2" t="s">

--- a/JsonConverter/ExcelFiles/CocktailRecipe.xlsx
+++ b/JsonConverter/ExcelFiles/CocktailRecipe.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="20610" windowHeight="11190"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="25545" windowHeight="11190"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -16,21 +16,21 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="93">
   <x:si>
+    <x:t>Cocktail_PianoMan_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BadTouch_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_ZenStar_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Suplex_2</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cocktail_GutPunch_2</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocktail_ZenStar_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Suplex_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_PianoMan_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BadTouch_2</x:t>
-  </x:si>
-  <x:si>
     <x:t>Cocktail_Piledriver_2</x:t>
   </x:si>
   <x:si>
@@ -40,37 +40,40 @@
     <x:t>Cocktail_FringeWeaver_2</x:t>
   </x:si>
   <x:si>
+    <x:t>Cocktail_CreviceSpike_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Mersblast_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_MoonBlast_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BloomLight_2</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cocktail_FrothyWater_2</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocktail_CreviceSpike_2</x:t>
-  </x:si>
-  <x:si>
     <x:t>Cocktail_PianoWoman_2</x:t>
   </x:si>
   <x:si>
     <x:t>Cocktail_SparkleStar_2</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocktail_Mersblast_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_MoonBlast_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BloomLight_2</x:t>
+    <x:t>Cocktail_Brandtini_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_SugarRush_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_CobaltVelvet_2</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Cocktail_Fail_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocktail_Brandtini_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_SugarRush_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_CobaltVelvet_2</x:t>
+    <x:t>Cocktail_BlueFairy_2</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Cocktail_Suplex_1</x:t>
@@ -88,163 +91,163 @@
     <x:t>Cocktail_FluffyDream_2</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocktail_BlueFairy_2</x:t>
+    <x:t>Cocktail_Fail_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Beer_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Age</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맥주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>젠스타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Flanergide</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Karmotrine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BronsonExt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Optional</x:t>
+  </x:si>
+  <x:si>
+    <x:t>크레바스 스파이크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Adelhyde</x:t>
+  </x:si>
+  <x:si>
+    <x:t>션샤인 클라우드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PwdDelta</x:t>
+  </x:si>
+  <x:si>
+    <x:t>머큐리 블라스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_CobaltVelvet_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_CreviceSpike_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_GrlzzlyTemple_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_SunshineCloud_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Mercuryblast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_BleedingJane_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_FringeWeaver_1</x:t>
   </x:si>
   <x:si>
     <x:t>스파클 스타</x:t>
   </x:si>
   <x:si>
+    <x:t>true</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블리딩 제인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코발트 벨벳</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 맨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슈가 러쉬</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 우먼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블룸 라이트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>문 블라스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F@####</x:t>
+  </x:si>
+  <x:si>
     <x:t>string</x:t>
   </x:si>
   <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>false</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블루 페어리</x:t>
+  </x:si>
+  <x:si>
     <x:t>프린지 위버</x:t>
   </x:si>
   <x:si>
+    <x:t>브랜티니</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거트 펀치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>플러피 드림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마스블라스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수플렉스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배드 터치</x:t>
+  </x:si>
+  <x:si>
     <x:t>프로씨 워터</x:t>
   </x:si>
   <x:si>
-    <x:t>마스블라스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>false</x:t>
-  </x:si>
-  <x:si>
-    <x:t>F@####</x:t>
-  </x:si>
-  <x:si>
-    <x:t>문 블라스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수플렉스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피아노 맨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블루 페어리</x:t>
-  </x:si>
-  <x:si>
     <x:t>파일 드라이버</x:t>
   </x:si>
   <x:si>
-    <x:t>브랜티니</x:t>
-  </x:si>
-  <x:si>
     <x:t>bool</x:t>
   </x:si>
   <x:si>
-    <x:t>피아노 우먼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거트 펀치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블리딩 제인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코발트 벨벳</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슈가 러쉬</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블룸 라이트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>true</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>플러피 드림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배드 터치</x:t>
-  </x:si>
-  <x:si>
     <x:t>그리즐리 템플</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocktail_Fail_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Beer_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Age</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>젠스타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맥주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_SunshineCloud_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Mercuryblast_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_CobaltVelvet_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_BleedingJane_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_FringeWeaver_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_CreviceSpike_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_GrlzzlyTemple_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>크레바스 스파이크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Flanergide</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Karmotrine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BronsonExt</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Optional</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PwdDelta</x:t>
-  </x:si>
-  <x:si>
-    <x:t>머큐리 블라스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Adelhyde</x:t>
-  </x:si>
-  <x:si>
-    <x:t>션샤인 클라우드</x:t>
+    <x:t>Icon/Cocktail_MoonBlast_1</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Cocktail_GutPunch_1</x:t>
@@ -253,9 +256,6 @@
     <x:t>Icon/Cocktail_Piledriver_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Cocktail_MoonBlast_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>Icon/Cocktail_SparkleStar_1</x:t>
   </x:si>
   <x:si>
@@ -268,31 +268,31 @@
     <x:t>Icon/Cocktail_FluffyDream_1</x:t>
   </x:si>
   <x:si>
+    <x:t>Icon/Cocktail_SugarRush_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_PianoWoman_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_BloomLight_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Icon/Cocktail_BlueFairy_1 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_GrlzzlyTemple_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_BadTouch_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_SunshineCloud_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_PianoMan_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>Icon/Cocktail_Marsblast_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_PianoWoman_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_SugarRush_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Icon/Cocktail_BlueFairy_1 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_BloomLight_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_GrlzzlyTemple_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_BadTouch_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_SunshineCloud_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_PianoMan_1</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -582,7 +582,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -665,7 +664,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -700,7 +698,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -745,7 +742,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -789,7 +785,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -874,7 +869,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -895,7 +889,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -926,7 +919,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1641,87 +1633,87 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:11" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="J2" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="K2" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11" s="11" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="10" t="s">
-        <x:v>58</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B3" s="10" t="s">
-        <x:v>45</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C3" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D3" s="13" t="s">
-        <x:v>71</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E3" s="13" t="s">
-        <x:v>73</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F3" s="13" t="s">
-        <x:v>68</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G3" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H3" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="I3" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="J3" s="13" t="s">
-        <x:v>72</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="K3" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>43</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C4" s="14">
         <x:v>2</x:v>
@@ -1739,26 +1731,26 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H4" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="I4" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J4" s="18" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K4" s="3" t="s">
-        <x:v>86</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="L4" s="4"/>
       <x:c r="M4" s="4"/>
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>25</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C5" s="15">
         <x:v>2</x:v>
@@ -1776,26 +1768,26 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H5" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="I5" s="18" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J5" s="18" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K5" s="3" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="L5" s="4"/>
-      <x:c r="M5" s="4"/>
+      <x:c r="M5" s="18"/>
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C6" s="15">
         <x:v>4</x:v>
@@ -1813,13 +1805,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H6" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="I6" s="18" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J6" s="18" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K6" s="5" t="s">
         <x:v>87</x:v>
@@ -1829,10 +1821,10 @@
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C7" s="17">
         <x:v>6</x:v>
@@ -1850,13 +1842,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H7" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="I7" s="18" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J7" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K7" s="6" t="s">
         <x:v>82</x:v>
@@ -1866,10 +1858,10 @@
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>39</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C8" s="17">
         <x:v>5</x:v>
@@ -1887,13 +1879,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H8" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="I8" s="18" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J8" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K8" s="6" t="s">
         <x:v>85</x:v>
@@ -1903,10 +1895,10 @@
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C9" s="17">
         <x:v>0</x:v>
@@ -1924,16 +1916,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H9" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="I9" s="18" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J9" s="18" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K9" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="L9" s="4"/>
       <x:c r="M9" s="4"/>
@@ -1943,7 +1935,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C10" s="14">
         <x:v>0</x:v>
@@ -1961,26 +1953,26 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="H10" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="I10" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J10" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K10" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="L10" s="4"/>
       <x:c r="M10" s="4"/>
     </x:row>
     <x:row r="11" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A11" s="6" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="6" t="s">
-        <x:v>33</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C11" s="14">
         <x:v>0</x:v>
@@ -1998,26 +1990,26 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H11" s="18" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I11" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J11" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K11" s="6" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L11" s="4"/>
       <x:c r="M11" s="4"/>
     </x:row>
     <x:row r="12" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A12" s="6" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B12" s="6" t="s">
-        <x:v>48</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C12" s="16">
         <x:v>3</x:v>
@@ -2035,13 +2027,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H12" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="I12" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J12" s="18" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K12" s="6" t="s">
         <x:v>83</x:v>
@@ -2051,10 +2043,10 @@
     </x:row>
     <x:row r="13" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A13" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C13" s="17">
         <x:v>0</x:v>
@@ -2072,26 +2064,26 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="H13" s="18" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I13" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J13" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K13" s="6" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="L13" s="4"/>
       <x:c r="M13" s="4"/>
     </x:row>
     <x:row r="14" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A14" s="6" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B14" s="7" t="s">
-        <x:v>56</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C14" s="14">
         <x:v>4</x:v>
@@ -2109,26 +2101,26 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="H14" s="18" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I14" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J14" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K14" s="6" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="L14" s="4"/>
       <x:c r="M14" s="4"/>
     </x:row>
     <x:row r="15" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A15" s="6" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C15" s="14">
         <x:v>4</x:v>
@@ -2146,26 +2138,26 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H15" s="18" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I15" s="18" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J15" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K15" s="6" t="s">
-        <x:v>88</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="L15" s="4"/>
       <x:c r="M15" s="4"/>
     </x:row>
     <x:row r="16" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A16" s="6" t="s">
-        <x:v>52</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B16" s="7" t="s">
-        <x:v>57</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C16" s="15">
         <x:v>1</x:v>
@@ -2183,24 +2175,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="H16" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="I16" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J16" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K16" s="6" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A17" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B17" s="7" t="s">
-        <x:v>28</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C17" s="15">
         <x:v>1</x:v>
@@ -2218,13 +2210,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H17" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="I17" s="18" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J17" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K17" s="6" t="s">
         <x:v>81</x:v>
@@ -2232,10 +2224,10 @@
     </x:row>
     <x:row r="18" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A18" s="6" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="7" t="s">
-        <x:v>42</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C18" s="15">
         <x:v>2</x:v>
@@ -2253,16 +2245,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="H18" s="18" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I18" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J18" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K18" s="6" t="s">
-        <x:v>61</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11" ht="15.75" customHeight="1">
@@ -2270,7 +2262,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B19" s="7" t="s">
-        <x:v>27</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C19" s="15">
         <x:v>1</x:v>
@@ -2288,24 +2280,24 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="H19" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="I19" s="18" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J19" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K19" s="6" t="s">
-        <x:v>63</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A20" s="6" t="s">
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B20" s="7" t="s">
-        <x:v>32</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C20" s="15">
         <x:v>6</x:v>
@@ -2323,24 +2315,24 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H20" s="18" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I20" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J20" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K20" s="6" t="s">
-        <x:v>79</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A21" s="6" t="s">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B21" s="7" t="s">
-        <x:v>50</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C21" s="15">
         <x:v>3</x:v>
@@ -2358,24 +2350,24 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H21" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="I21" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J21" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K21" s="6" t="s">
-        <x:v>65</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A22" s="6" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B22" s="7" t="s">
-        <x:v>76</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C22" s="15">
         <x:v>2</x:v>
@@ -2393,24 +2385,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H22" s="18" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I22" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J22" s="18" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K22" s="6" t="s">
-        <x:v>59</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A23" s="6" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B23" s="7" t="s">
-        <x:v>67</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C23" s="15">
         <x:v>0</x:v>
@@ -2428,24 +2420,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H23" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="I23" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J23" s="18" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K23" s="6" t="s">
-        <x:v>64</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A24" s="6" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B24" s="7" t="s">
-        <x:v>74</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C24" s="15">
         <x:v>1</x:v>
@@ -2463,24 +2455,24 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H24" s="18" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I24" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J24" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K24" s="6" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A25" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B25" s="7" t="s">
-        <x:v>34</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C25" s="15">
         <x:v>2</x:v>
@@ -2498,16 +2490,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H25" s="18" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I25" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J25" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K25" s="6" t="s">
-        <x:v>92</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11" ht="15.75" customHeight="1">
@@ -2515,7 +2507,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B26" s="8" t="s">
-        <x:v>41</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C26" s="16">
         <x:v>0</x:v>
@@ -2533,24 +2525,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H26" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="I26" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J26" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K26" s="6" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A27" s="6" t="s">
-        <x:v>12</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B27" s="8" t="s">
-        <x:v>29</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C27" s="16">
         <x:v>0</x:v>
@@ -2568,28 +2560,28 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H27" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="I27" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J27" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K27" s="6" t="s">
-        <x:v>84</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A28" s="19" t="s">
-        <x:v>51</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B28" s="8" t="s">
-        <x:v>31</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C28" s="8"/>
       <x:c r="K28" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3" ht="15.75" customHeight="1">
